--- a/cases-template.xlsx
+++ b/cases-template.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -108,6 +108,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -519,59 +522,90 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Sisa cuti tahunan</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Berapa sisa cuti tahunan saya?</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Berikut ringkasan **cuti tahunan** Anda untuk 2026:
-- Kuota tahunan: **12 hari**
-- Sudah terpakai: **5 hari**
-- **Sisa: 7 hari**
-Ingin saya bantu membuat pengajuan cuti?</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Berikut ringkasan **cuti tahunan** Anda untuk 2026:</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Saldo konsisten (kuota − terpakai = sisa). Jangan mengarang angka tanpa data karyawan. Tawarkan tindak lanjut.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Komponen | Jumlah
+Kuota tahunan | 12 hari
+Sudah terpakai | 5 hari
+Sisa | 7 hari</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>markdown</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Ingin saya bantu membuat pengajuan cuti?</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Daftar jenis cuti</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Jenis cuti apa saja yang tersedia?</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Jenis Cuti | Kuota | Perlu Persetujuan
 Cuti Tahunan | 12 hari/tahun | Atasan langsung
@@ -580,77 +614,32 @@
 Cuti Penting | 2 hari/kejadian | Atasan langsung</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Sertakan semua jenis cuti aktif beserta kuota dan jalur persetujuan.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="6">
+      <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Pengajuan cuti (A2UI)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Saya mau mengajukan cuti tahunan</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>a2ui</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>[
-  {"version":"v0.9","createSurface":{"surfaceId":"leave","catalogId":"https://a2ui.org/catalogs/basic/catalog.json","theme":{"primaryColor":"#006f9e","agentDisplayName":"Employee Assistant"}}},
-  {"version":"v0.9","updateComponents":{"surfaceId":"leave","components":[
-    {"id":"root","component":"Card","child":"col"},
-    {"id":"col","component":"Column","children":["title","type_label","type_picker","reason_label","reason_field","note","submit"]},
-    {"id":"title","component":"Text","text":"# Pengajuan Cuti Tahunan","variant":"h2"},
-    {"id":"type_label","component":"Text","text":"Jenis cuti","variant":"caption"},
-    {"id":"type_picker","component":"ChoicePicker","variant":"mutuallyExclusive","options":[{"label":"Cuti Tahunan","value":"annual"},{"label":"Cuti Penting","value":"important"}],"value":{"path":"/leave/type"}},
-    {"id":"reason_label","component":"Text","text":"Alasan","variant":"caption"},
-    {"id":"reason_field","component":"TextField","label":"Alasan cuti","value":{"path":"/leave/reason"},"checks":[{"call":"required","args":{"value":{"path":"/leave/reason"}},"message":"Alasan wajib diisi."}]},
-    {"id":"note","component":"Text","text":"Pengajuan dikirim ke atasan langsung untuk persetujuan.","variant":"caption"},
-    {"id":"submit","component":"Button","child":"submit_label","variant":"primary","action":{"event":{"name":"submit_leave_request","context":{"type":{"path":"/leave/type"},"reason":{"path":"/leave/reason"}}}}},
-    {"id":"submit_label","component":"Text","text":"Kirim pengajuan"}
-  ]}},
-  {"version":"v0.9","updateDataModel":{"surfaceId":"leave","path":"/leave","value":{"type":["annual"],"reason":""}}}
-]</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Render form pengajuan. Aksi utama 'submit_leave_request'. Field 'alasan' wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Quick replies</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Apa yang bisa saya lakukan?</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>buttons</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Ajukan ketidakhadiran | submit_absence
 Ajukan koreksi kehadiran | submit_attendance_correction
@@ -658,7 +647,7 @@
 Ajukan cuti tahunan | submit_annual_leave</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Empat quick-reply sesuai intent utama Employee Assistant.</t>
         </is>
@@ -680,232 +669,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Setting (key)</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>productName</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Claudia</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Shown in the chat header</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>proyekName</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Employee Assistant</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sidebar project name</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>assistantName</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Asisten Virtual HR</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Subtitle under the product name</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>proyekDesc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- Help you submit requests, approve requests (manager only), and answer employee related inquiries.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Description under the hero (screen 1)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>modelName</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>GPT 5.5</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Model label shown on each assistant answer (e.g. 'Claude Sonnet 4')</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>llmName</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Model shown/used when no Agen AI is active</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>userName</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Label for the user</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>activeAgent</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>browser-use</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Active agent id ("" = use the LLM)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>assistantAvatar</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>(set in app)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Emoji / image URL / data-URI. App ships with the Claudia logo.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>activeConversation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Active conversation id</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>userAvatar</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>🙂</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Emoji OR image URL</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>primaryHsl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Optional primary override "H S% L%"</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>#006f9e</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Catapa/Claudia primary blue</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"name": "Annisa'ur Rosi Lutfiana", "email": "annisaur.r.lutfiana@gdplabs.id", "picture": ""}</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JSON {name,email,picture}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>userBubble</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>#eceef0</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>User message bubble (light grey, Claude-style)</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>agents</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[{"id": "browser-use", "name": "Browser Use Agent"}, {"id": "code-interpreter", "name": "Code Interpreter Agent"}, {"id": "gl-calendly", "name": "GL Calendly Agent"}]</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JSON [{id,name}] (max 3)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>bg</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>#ffffff</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Chat background</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>conversations</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[{"id": "c1", "title": "Pengajuan Cuti &amp; Pertanyaan HR"}, {"id": "c2", "title": "Table Generation Request"}, {"id": "c3", "title": "Jadwal Kosong Mahesa Hari Ini"}]</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JSON [{id,title}] (left sidebar)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>surface</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>#f5f5f5</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Muted surface / typing indicator</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>shortcuts</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[{"id": "s1", "text": "Saya mau mengajukan ketidakhadiran"}, {"id": "s2", "text": "Saya mau mengajukan koreksi kehadiran"}, {"id": "s3", "text": "Cek pengajuan yang harus saya setujui"}, {"id": "s4", "text": "Saya mau mengajukan cuti tahunan"}]</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JSON [{id,text}] (screen-1 chips, max 4)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>ink</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>#1c1c1c</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Main text color</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>font</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>"Inter","Open Sans",system-ui,sans-serif</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>App font stack</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>prepSteps</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[{"id": "p1", "text": "Memahami pesan pengguna"}, {"id": "p2", "text": "Mengambil data"}]</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JSON [{id,text}] (loader steps)</t>
         </is>
       </c>
     </row>
@@ -920,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -929,7 +892,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Chat Case Studio — authoring template (Claudia skin)</t>
+          <t>Static Chat Generator — authoring template (Claudia skin)</t>
         </is>
       </c>
     </row>
@@ -987,7 +950,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>3. Open index.html → Import .xlsx → choose this file. Press Play to preview/record; Export for the dev spec.</t>
+          <t>3. Open index.html → Import .xlsx → choose this file. Press Play to preview/record.</t>
         </is>
       </c>
     </row>
@@ -1026,6 +989,34 @@
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  a2ui     : A2UI v0.9 envelopes as a JSON array (or one JSON object per line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Multi-part answers (e.g. text → table → text):</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     • Add extra rows directly below a case and LEAVE 'User Prompt' BLANK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     • Each blank-prompt row adds another response block (its own Response Type + Response).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     • Blocks play in order, top to bottom, within that one answer.</t>
         </is>
       </c>
     </row>
